--- a/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Payroll 2026-07.xlsx
+++ b/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Payroll 2026-07.xlsx
@@ -765,7 +765,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5B4636"/>
+        <fgColor rgb="FF321E1E"/>
       </patternFill>
     </fill>
   </fills>

--- a/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Payroll 2026-07.xlsx
+++ b/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Payroll 2026-07.xlsx
@@ -133,466 +133,586 @@
     <t>SDH-1006</t>
   </si>
   <si>
+    <t>Saad Al Shammari</t>
+  </si>
+  <si>
+    <t>Marketing and Communications</t>
+  </si>
+  <si>
+    <t>SA74 1015 9796 0906 4373 7913</t>
+  </si>
+  <si>
+    <t>SDH-1007</t>
+  </si>
+  <si>
+    <t>Nasser Al Qahtani</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Alinma Bank</t>
+  </si>
+  <si>
+    <t>SA71 0581 3560 5224 2244 1140</t>
+  </si>
+  <si>
+    <t>SDH-1008</t>
+  </si>
+  <si>
+    <t>Anas Al Qurashi</t>
+  </si>
+  <si>
+    <t>Hospitality and Guest Experience</t>
+  </si>
+  <si>
+    <t>G06</t>
+  </si>
+  <si>
+    <t>SA48 8073 7054 4758 6232 5374</t>
+  </si>
+  <si>
+    <t>SDH-1009</t>
+  </si>
+  <si>
+    <t>Osama Al Tamimi</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>Bank Albilad</t>
+  </si>
+  <si>
+    <t>SA02 1502 9991 9344 1209 4224</t>
+  </si>
+  <si>
+    <t>SDH-1010</t>
+  </si>
+  <si>
+    <t>Amal Al Yami</t>
+  </si>
+  <si>
+    <t>Destination Development</t>
+  </si>
+  <si>
+    <t>SA31 8075 1639 3577 3341 1935</t>
+  </si>
+  <si>
+    <t>SDH-1011</t>
+  </si>
+  <si>
+    <t>Vikram Chowdhury</t>
+  </si>
+  <si>
+    <t>Heritage and Culture</t>
+  </si>
+  <si>
+    <t>SA82 8022 9750 9693 8182 0203</t>
+  </si>
+  <si>
+    <t>SDH-1012</t>
+  </si>
+  <si>
+    <t>Fahad Al Anazi</t>
+  </si>
+  <si>
+    <t>G13</t>
+  </si>
+  <si>
+    <t>Riyad Bank</t>
+  </si>
+  <si>
+    <t>SA17 2093 7556 1296 7851 5955</t>
+  </si>
+  <si>
+    <t>SDH-1013</t>
+  </si>
+  <si>
+    <t>Khalid Al Juhani</t>
+  </si>
+  <si>
+    <t>Site Operations and Safety</t>
+  </si>
+  <si>
+    <t>G04</t>
+  </si>
+  <si>
+    <t>SA74 0513 0466 0168 1719 4873</t>
+  </si>
+  <si>
+    <t>SDH-1014</t>
+  </si>
+  <si>
+    <t>Abdulaziz Al Tamimi</t>
+  </si>
+  <si>
+    <t>G05</t>
+  </si>
+  <si>
+    <t>SA22 5519 7066 0809 2659 3456</t>
+  </si>
+  <si>
+    <t>SDH-1015</t>
+  </si>
+  <si>
+    <t>Nikhil Menon</t>
+  </si>
+  <si>
+    <t>SA34 8072 2320 4906 7464 9695</t>
+  </si>
+  <si>
+    <t>SDH-1016</t>
+  </si>
+  <si>
+    <t>Noura Al Subaie</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>SA51 8069 0045 5116 3998 6462</t>
+  </si>
+  <si>
+    <t>SDH-1017</t>
+  </si>
+  <si>
+    <t>Hamad Al Sudairi</t>
+  </si>
+  <si>
+    <t>SA84 1077 2195 8381 3929 3814</t>
+  </si>
+  <si>
+    <t>SDH-1018</t>
+  </si>
+  <si>
+    <t>Badr Al Fahad</t>
+  </si>
+  <si>
+    <t>Executive Office</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>SA02 1593 6986 0458 5089 1806</t>
+  </si>
+  <si>
+    <t>SDH-1019</t>
+  </si>
+  <si>
+    <t>Sami Shawky</t>
+  </si>
+  <si>
+    <t>SA68 8059 7460 4428 9894 0500</t>
+  </si>
+  <si>
+    <t>SDH-1020</t>
+  </si>
+  <si>
+    <t>Haifa Al Asmari</t>
+  </si>
+  <si>
+    <t>SA25 5548 3534 0958 4480 8611</t>
+  </si>
+  <si>
+    <t>SDH-1021</t>
+  </si>
+  <si>
+    <t>Mohammed Al Shehri</t>
+  </si>
+  <si>
+    <t>SA38 1052 5045 9035 3248 7743</t>
+  </si>
+  <si>
+    <t>SDH-1022</t>
+  </si>
+  <si>
+    <t>Saad Al Subaie</t>
+  </si>
+  <si>
+    <t>SA88 1097 5658 5254 1597 5075</t>
+  </si>
+  <si>
+    <t>SDH-1023</t>
+  </si>
+  <si>
+    <t>Ziyad Al Shammari</t>
+  </si>
+  <si>
+    <t>G07</t>
+  </si>
+  <si>
+    <t>SA20 5533 8095 9213 5231 8752</t>
+  </si>
+  <si>
+    <t>SDH-1024</t>
+  </si>
+  <si>
+    <t>Vikram DSouza</t>
+  </si>
+  <si>
+    <t>SA78 8070 0066 1243 1135 0867</t>
+  </si>
+  <si>
+    <t>SDH-1025</t>
+  </si>
+  <si>
+    <t>Abdulrahman Al Asmari</t>
+  </si>
+  <si>
+    <t>SA10 2018 6018 7941 9540 3471</t>
+  </si>
+  <si>
+    <t>SDH-1026</t>
+  </si>
+  <si>
+    <t>Faisal Al Mutairi</t>
+  </si>
+  <si>
+    <t>SA39 0559 9198 1342 7476 4054</t>
+  </si>
+  <si>
+    <t>SDH-1027</t>
+  </si>
+  <si>
+    <t>Jose Santos</t>
+  </si>
+  <si>
+    <t>SA55 1011 9486 5565 8805 5406</t>
+  </si>
+  <si>
+    <t>SDH-1028</t>
+  </si>
+  <si>
+    <t>Khalid Al Subaie</t>
+  </si>
+  <si>
+    <t>SA65 2088 7126 9647 8566 1113</t>
+  </si>
+  <si>
+    <t>SDH-1029</t>
+  </si>
+  <si>
+    <t>Saad Al Saud</t>
+  </si>
+  <si>
+    <t>SA06 8083 3733 2380 8236 6836</t>
+  </si>
+  <si>
+    <t>SDH-1030</t>
+  </si>
+  <si>
+    <t>Lulwa Al Rasheed</t>
+  </si>
+  <si>
+    <t>SA16 1013 9706 2308 4382 5668</t>
+  </si>
+  <si>
+    <t>SDH-1031</t>
+  </si>
+  <si>
+    <t>Mansour Al Sudairi</t>
+  </si>
+  <si>
+    <t>SA90 1017 3689 2972 1801 9961</t>
+  </si>
+  <si>
+    <t>SDH-1032</t>
+  </si>
+  <si>
+    <t>Badr Al Sheikh</t>
+  </si>
+  <si>
+    <t>SA78 8085 5724 4267 1712 8160</t>
+  </si>
+  <si>
+    <t>SDH-1033</t>
+  </si>
+  <si>
+    <t>Sara Al Otaibi</t>
+  </si>
+  <si>
+    <t>SA07 1048 6097 3331 8814 0152</t>
+  </si>
+  <si>
+    <t>SDH-1034</t>
+  </si>
+  <si>
+    <t>Haifa Al Qurashi</t>
+  </si>
+  <si>
+    <t>SA56 2007 7107 2019 7901 6420</t>
+  </si>
+  <si>
+    <t>SDH-1035</t>
+  </si>
+  <si>
+    <t>Mostafa Gemayel</t>
+  </si>
+  <si>
+    <t>SA74 1528 4462 3382 2177 0474</t>
+  </si>
+  <si>
+    <t>SDH-1036</t>
+  </si>
+  <si>
+    <t>Anas Al Malki</t>
+  </si>
+  <si>
+    <t>SA24 8097 0190 1901 2751 8670</t>
+  </si>
+  <si>
+    <t>SDH-1037</t>
+  </si>
+  <si>
+    <t>Walid Haddad</t>
+  </si>
+  <si>
+    <t>SA88 8050 0521 4714 1300 4516</t>
+  </si>
+  <si>
+    <t>SDH-1038</t>
+  </si>
+  <si>
+    <t>Priya Hossain</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>SA37 1077 7932 3673 1773 4684</t>
+  </si>
+  <si>
+    <t>SDH-1039</t>
+  </si>
+  <si>
+    <t>Deema Al Subaie</t>
+  </si>
+  <si>
+    <t>SA28 1008 1703 6892 0900 0859</t>
+  </si>
+  <si>
+    <t>SDH-1040</t>
+  </si>
+  <si>
+    <t>Badr Al Anazi</t>
+  </si>
+  <si>
+    <t>SA84 5500 8135 3636 9403 6675</t>
+  </si>
+  <si>
+    <t>SDH-1041</t>
+  </si>
+  <si>
+    <t>Abeer Al Juhani</t>
+  </si>
+  <si>
+    <t>SA53 8036 8142 2247 3554 2870</t>
+  </si>
+  <si>
+    <t>Yazeed Al Shammari</t>
+  </si>
+  <si>
+    <t>SA92 1568 7029 4565 5318 7753</t>
+  </si>
+  <si>
+    <t>SDH-1043</t>
+  </si>
+  <si>
+    <t>Bandar Al Rashidi</t>
+  </si>
+  <si>
+    <t>SA62 2034 1895 7380 3834 9996</t>
+  </si>
+  <si>
+    <t>SDH-1044</t>
+  </si>
+  <si>
+    <t>Angela Cruz</t>
+  </si>
+  <si>
+    <t>SA06 1050 8179 3304 3915 4304</t>
+  </si>
+  <si>
+    <t>SDH-1045</t>
+  </si>
+  <si>
+    <t>Nasser Al Muqbel</t>
+  </si>
+  <si>
+    <t>SA52 1022 0482 1074 6859 0026</t>
+  </si>
+  <si>
+    <t>SDH-1046</t>
+  </si>
+  <si>
+    <t>Anas Al Otaibi</t>
+  </si>
+  <si>
+    <t>SA59 5509 6461 8984 8740 2837</t>
+  </si>
+  <si>
+    <t>SDH-1047</t>
+  </si>
+  <si>
+    <t>Hessa Al Subaie</t>
+  </si>
+  <si>
+    <t>SA66 8043 2353 8554 8342 9002</t>
+  </si>
+  <si>
+    <t>SDH-1048</t>
+  </si>
+  <si>
+    <t>Hamad Al Saud</t>
+  </si>
+  <si>
+    <t>Saudi Awwal Bank</t>
+  </si>
+  <si>
+    <t>SA73 4546 2431 3560 6993 2540</t>
+  </si>
+  <si>
+    <t>SDH-1049</t>
+  </si>
+  <si>
+    <t>Angela Santos</t>
+  </si>
+  <si>
+    <t>SA73 0566 4739 7230 6355 2201</t>
+  </si>
+  <si>
+    <t>SDH-1050</t>
+  </si>
+  <si>
+    <t>Nawaf Al Ghamdi</t>
+  </si>
+  <si>
+    <t>SA31 2006 8926 6125 6171 2001</t>
+  </si>
+  <si>
+    <t>SDH-1051</t>
+  </si>
+  <si>
     <t>Mishari Al Rasheed</t>
   </si>
   <si>
     <t>SA25 8093 1672 3598 2012 8179</t>
   </si>
   <si>
-    <t>SDH-1007</t>
-  </si>
-  <si>
-    <t>Saad Al Shammari</t>
-  </si>
-  <si>
-    <t>Marketing and Communications</t>
-  </si>
-  <si>
-    <t>SA74 1015 9796 0906 4373 7913</t>
-  </si>
-  <si>
-    <t>SDH-1008</t>
-  </si>
-  <si>
-    <t>Nasser Al Qahtani</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Alinma Bank</t>
-  </si>
-  <si>
-    <t>SA71 0581 3560 5224 2244 1140</t>
-  </si>
-  <si>
-    <t>SDH-1009</t>
-  </si>
-  <si>
-    <t>Anas Al Qurashi</t>
-  </si>
-  <si>
-    <t>Hospitality and Guest Experience</t>
-  </si>
-  <si>
-    <t>G06</t>
-  </si>
-  <si>
-    <t>SA48 8073 7054 4758 6232 5374</t>
-  </si>
-  <si>
-    <t>SDH-1010</t>
-  </si>
-  <si>
-    <t>Osama Al Tamimi</t>
-  </si>
-  <si>
-    <t>G12</t>
-  </si>
-  <si>
-    <t>Bank Albilad</t>
-  </si>
-  <si>
-    <t>SA02 1502 9991 9344 1209 4224</t>
-  </si>
-  <si>
-    <t>SDH-1011</t>
-  </si>
-  <si>
-    <t>Amal Al Yami</t>
-  </si>
-  <si>
-    <t>Destination Development</t>
-  </si>
-  <si>
-    <t>SA31 8075 1639 3577 3341 1935</t>
-  </si>
-  <si>
-    <t>SDH-1012</t>
-  </si>
-  <si>
-    <t>Vikram Chowdhury</t>
-  </si>
-  <si>
-    <t>Heritage and Culture</t>
-  </si>
-  <si>
-    <t>SA82 8022 9750 9693 8182 0203</t>
-  </si>
-  <si>
-    <t>SDH-1013</t>
-  </si>
-  <si>
-    <t>Fahad Al Anazi</t>
-  </si>
-  <si>
-    <t>G13</t>
-  </si>
-  <si>
-    <t>Riyad Bank</t>
-  </si>
-  <si>
-    <t>SA17 2093 7556 1296 7851 5955</t>
-  </si>
-  <si>
-    <t>SDH-1014</t>
-  </si>
-  <si>
-    <t>Khalid Al Juhani</t>
-  </si>
-  <si>
-    <t>Site Operations and Safety</t>
-  </si>
-  <si>
-    <t>G04</t>
-  </si>
-  <si>
-    <t>SA74 0513 0466 0168 1719 4873</t>
-  </si>
-  <si>
-    <t>SDH-1015</t>
-  </si>
-  <si>
-    <t>Abdulaziz Al Tamimi</t>
-  </si>
-  <si>
-    <t>G05</t>
-  </si>
-  <si>
-    <t>SA22 5519 7066 0809 2659 3456</t>
-  </si>
-  <si>
-    <t>SDH-1016</t>
-  </si>
-  <si>
-    <t>Nikhil Menon</t>
-  </si>
-  <si>
-    <t>SA34 8072 2320 4906 7464 9695</t>
-  </si>
-  <si>
-    <t>SDH-1017</t>
-  </si>
-  <si>
-    <t>Noura Al Subaie</t>
-  </si>
-  <si>
-    <t>G10</t>
-  </si>
-  <si>
-    <t>SA51 8069 0045 5116 3998 6462</t>
-  </si>
-  <si>
-    <t>SDH-1018</t>
-  </si>
-  <si>
-    <t>Hamad Al Sudairi</t>
-  </si>
-  <si>
-    <t>SA84 1077 2195 8381 3929 3814</t>
-  </si>
-  <si>
-    <t>SDH-1019</t>
-  </si>
-  <si>
-    <t>Badr Al Fahad</t>
-  </si>
-  <si>
-    <t>Executive Office</t>
-  </si>
-  <si>
-    <t>G15</t>
-  </si>
-  <si>
-    <t>SA02 1593 6986 0458 5089 1806</t>
-  </si>
-  <si>
-    <t>SDH-1020</t>
-  </si>
-  <si>
-    <t>Sami Shawky</t>
-  </si>
-  <si>
-    <t>SA68 8059 7460 4428 9894 0500</t>
-  </si>
-  <si>
-    <t>SDH-1021</t>
-  </si>
-  <si>
-    <t>Haifa Al Asmari</t>
-  </si>
-  <si>
-    <t>SA25 5548 3534 0958 4480 8611</t>
-  </si>
-  <si>
-    <t>SDH-1022</t>
-  </si>
-  <si>
-    <t>Mohammed Al Shehri</t>
-  </si>
-  <si>
-    <t>SA38 1052 5045 9035 3248 7743</t>
-  </si>
-  <si>
-    <t>SDH-1023</t>
-  </si>
-  <si>
-    <t>Saad Al Subaie</t>
-  </si>
-  <si>
-    <t>SA88 1097 5658 5254 1597 5075</t>
-  </si>
-  <si>
-    <t>SDH-1024</t>
-  </si>
-  <si>
-    <t>Ziyad Al Shammari</t>
-  </si>
-  <si>
-    <t>G07</t>
-  </si>
-  <si>
-    <t>SA20 5533 8095 9213 5231 8752</t>
-  </si>
-  <si>
-    <t>SDH-1025</t>
-  </si>
-  <si>
-    <t>Vikram DSouza</t>
-  </si>
-  <si>
-    <t>SA78 8070 0066 1243 1135 0867</t>
-  </si>
-  <si>
-    <t>Abdulrahman Al Asmari</t>
-  </si>
-  <si>
-    <t>SA10 2018 6018 7941 9540 3471</t>
-  </si>
-  <si>
-    <t>SDH-1027</t>
-  </si>
-  <si>
-    <t>Faisal Al Mutairi</t>
-  </si>
-  <si>
-    <t>SA39 0559 9198 1342 7476 4054</t>
-  </si>
-  <si>
-    <t>SDH-1028</t>
-  </si>
-  <si>
-    <t>Jose Santos</t>
-  </si>
-  <si>
-    <t>SA55 1011 9486 5565 8805 5406</t>
-  </si>
-  <si>
-    <t>SDH-1029</t>
-  </si>
-  <si>
-    <t>Khalid Al Subaie</t>
-  </si>
-  <si>
-    <t>SA65 2088 7126 9647 8566 1113</t>
-  </si>
-  <si>
-    <t>SDH-1030</t>
-  </si>
-  <si>
-    <t>Saad Al Saud</t>
-  </si>
-  <si>
-    <t>SA06 8083 3733 2380 8236 6836</t>
-  </si>
-  <si>
-    <t>SDH-1031</t>
-  </si>
-  <si>
-    <t>Lulwa Al Rasheed</t>
-  </si>
-  <si>
-    <t>SA16 1013 9706 2308 4382 5668</t>
-  </si>
-  <si>
-    <t>SDH-1032</t>
-  </si>
-  <si>
-    <t>Mansour Al Sudairi</t>
-  </si>
-  <si>
-    <t>SA90 1017 3689 2972 1801 9961</t>
-  </si>
-  <si>
-    <t>SDH-1033</t>
-  </si>
-  <si>
-    <t>Badr Al Sheikh</t>
-  </si>
-  <si>
-    <t>SA78 8085 5724 4267 1712 8160</t>
-  </si>
-  <si>
-    <t>SDH-1034</t>
-  </si>
-  <si>
-    <t>Sara Al Otaibi</t>
-  </si>
-  <si>
-    <t>SA07 1048 6097 3331 8814 0152</t>
-  </si>
-  <si>
-    <t>SDH-1035</t>
-  </si>
-  <si>
-    <t>Haifa Al Qurashi</t>
-  </si>
-  <si>
-    <t>SA56 2007 7170 2019 7901 6420</t>
-  </si>
-  <si>
-    <t>SDH-1036</t>
-  </si>
-  <si>
-    <t>Mostafa Gemayel</t>
-  </si>
-  <si>
-    <t>SA74 1528 4426 3382 2177 0474</t>
-  </si>
-  <si>
-    <t>SDH-1037</t>
-  </si>
-  <si>
-    <t>Anas Al Malki</t>
-  </si>
-  <si>
-    <t>SA24 8097 0190 1901 2751 8670</t>
-  </si>
-  <si>
-    <t>SDH-1038</t>
-  </si>
-  <si>
-    <t>Walid Haddad</t>
-  </si>
-  <si>
-    <t>SA88 8050 0521 4714 1300 4516</t>
-  </si>
-  <si>
-    <t>SDH-1039</t>
-  </si>
-  <si>
-    <t>Priya Hossain</t>
-  </si>
-  <si>
-    <t>Information Technology</t>
-  </si>
-  <si>
-    <t>SA37 1077 7932 3673 1773 4684</t>
-  </si>
-  <si>
-    <t>SDH-1040</t>
-  </si>
-  <si>
-    <t>Deema Al Subaie</t>
-  </si>
-  <si>
-    <t>SA28 1008 1703 6892 0900 0859</t>
-  </si>
-  <si>
-    <t>SDH-1041</t>
-  </si>
-  <si>
-    <t>Badr Al Anazi</t>
-  </si>
-  <si>
-    <t>SA84 5500 8135 3636 9403 6675</t>
-  </si>
-  <si>
-    <t>SDH-1042</t>
-  </si>
-  <si>
-    <t>Abeer Al Juhani</t>
-  </si>
-  <si>
-    <t>SA53 8036 8142 2247 3554 2870</t>
-  </si>
-  <si>
-    <t>SDH-1043</t>
-  </si>
-  <si>
-    <t>Yazeed Al Shammari</t>
-  </si>
-  <si>
-    <t>SA92 1568 7029 4565 5318 7753</t>
-  </si>
-  <si>
-    <t>SDH-1044</t>
-  </si>
-  <si>
-    <t>Bandar Al Rashidi</t>
-  </si>
-  <si>
-    <t>SA62 2034 1895 7380 3834 9996</t>
-  </si>
-  <si>
-    <t>SDH-1045</t>
-  </si>
-  <si>
-    <t>Angela Cruz</t>
-  </si>
-  <si>
-    <t>SA06 1050 8179 3304 3915 4304</t>
-  </si>
-  <si>
-    <t>SDH-1046</t>
-  </si>
-  <si>
-    <t>Anas Al Otaibi</t>
-  </si>
-  <si>
-    <t>SA59 5509 6461 8984 8740 2837</t>
-  </si>
-  <si>
-    <t>SDH-1047</t>
-  </si>
-  <si>
-    <t>Hessa Al Subaie</t>
-  </si>
-  <si>
-    <t>SA66 8043 2353 8554 8342 9002</t>
-  </si>
-  <si>
-    <t>SDH-1048</t>
-  </si>
-  <si>
-    <t>Hamad Al Saud</t>
-  </si>
-  <si>
-    <t>Saudi Awwal Bank</t>
-  </si>
-  <si>
-    <t>SA73 4546 2431 3560 6993 2540</t>
-  </si>
-  <si>
-    <t>SDH-1049</t>
-  </si>
-  <si>
-    <t>Angela Santos</t>
-  </si>
-  <si>
-    <t>SA73 0566 4739 7230 6355 2201</t>
-  </si>
-  <si>
-    <t>SDH-1050</t>
-  </si>
-  <si>
-    <t>Nawaf Al Ghamdi</t>
-  </si>
-  <si>
-    <t>SA31 2006 8926 6125 6171 2001</t>
-  </si>
-  <si>
-    <t>SDH-1051</t>
+    <t>SDH-1052</t>
+  </si>
+  <si>
+    <t>Tarek Abdelaziz</t>
+  </si>
+  <si>
+    <t>SA25 8017 1356 2223 5224 6689</t>
+  </si>
+  <si>
+    <t>SDH-1053</t>
+  </si>
+  <si>
+    <t>Waleed Al Harbi</t>
+  </si>
+  <si>
+    <t>SA69 8096 4160 9243 4510 6802</t>
+  </si>
+  <si>
+    <t>SDH-1054</t>
+  </si>
+  <si>
+    <t>Hani Masri</t>
+  </si>
+  <si>
+    <t>SA76 1072 6137 8234 1400 1401</t>
+  </si>
+  <si>
+    <t>SDH-1055</t>
+  </si>
+  <si>
+    <t>Nasser Al Zahrani</t>
+  </si>
+  <si>
+    <t>SA93 8026 0902 9791 8336 2638</t>
+  </si>
+  <si>
+    <t>SDH-1056</t>
+  </si>
+  <si>
+    <t>Grace Bautista</t>
+  </si>
+  <si>
+    <t>SA37 1065 1914 4120 2136 3305</t>
+  </si>
+  <si>
+    <t>SDH-1057</t>
+  </si>
+  <si>
+    <t>Fahad Al Saud</t>
+  </si>
+  <si>
+    <t>SA22 1562 3449 4229 3834 1589</t>
+  </si>
+  <si>
+    <t>SDH-1058</t>
+  </si>
+  <si>
+    <t>Anas Al Muqbel</t>
+  </si>
+  <si>
+    <t>SA21 8024 2073 4415 2676 3067</t>
+  </si>
+  <si>
+    <t>SDH-1059</t>
+  </si>
+  <si>
+    <t>Ibrahim Al Mutairi</t>
+  </si>
+  <si>
+    <t>SA51 2060 7139 3481 5189 8975</t>
+  </si>
+  <si>
+    <t>SDH-1060</t>
+  </si>
+  <si>
+    <t>Neha Siddiqui</t>
+  </si>
+  <si>
+    <t>SA37 0575 6452 7477 0178 5577</t>
+  </si>
+  <si>
+    <t>SDH-1061</t>
+  </si>
+  <si>
+    <t>Rakan Al Nasser</t>
+  </si>
+  <si>
+    <t>SA47 1049 9488 0092 5655 7314</t>
+  </si>
+  <si>
+    <t>SDH-1062</t>
+  </si>
+  <si>
+    <t>Munira Al Yami</t>
+  </si>
+  <si>
+    <t>SA41 2046 0003 4983 3392 0695</t>
+  </si>
+  <si>
+    <t>SDH-1063</t>
+  </si>
+  <si>
+    <t>Munira Al Asmari</t>
+  </si>
+  <si>
+    <t>Government Relations</t>
+  </si>
+  <si>
+    <t>SA97 1049 1927 9686 2893 2457</t>
+  </si>
+  <si>
+    <t>SDH-1064</t>
   </si>
   <si>
     <t>Ghadah Al Otaibi</t>
@@ -601,130 +721,10 @@
     <t>SA45 8093 5057 1515 2851 6337</t>
   </si>
   <si>
-    <t>SDH-1052</t>
-  </si>
-  <si>
-    <t>Tarek Abdelaziz</t>
-  </si>
-  <si>
-    <t>SA25 8017 1356 2223 5224 6689</t>
-  </si>
-  <si>
-    <t>SDH-1053</t>
-  </si>
-  <si>
-    <t>Waleed Al Harbi</t>
-  </si>
-  <si>
-    <t>SA69 8096 4160 9243 4510 6802</t>
-  </si>
-  <si>
-    <t>SDH-1054</t>
-  </si>
-  <si>
-    <t>Hani Masri</t>
-  </si>
-  <si>
-    <t>SA76 1072 6137 8234 1400 1401</t>
-  </si>
-  <si>
-    <t>SDH-1055</t>
-  </si>
-  <si>
-    <t>Nasser Al Zahrani</t>
-  </si>
-  <si>
-    <t>SA93 8026 0902 9791 8336 2638</t>
-  </si>
-  <si>
-    <t>SDH-1056</t>
-  </si>
-  <si>
-    <t>Grace Bautista</t>
-  </si>
-  <si>
-    <t>SA37 1065 1914 4120 2136 3305</t>
-  </si>
-  <si>
-    <t>SDH-1057</t>
-  </si>
-  <si>
-    <t>Fahad Al Saud</t>
-  </si>
-  <si>
-    <t>SA22 1562 3449 4229 3834 1589</t>
-  </si>
-  <si>
-    <t>SDH-1058</t>
-  </si>
-  <si>
-    <t>Anas Al Muqbel</t>
-  </si>
-  <si>
-    <t>SA21 8024 2073 4415 2676 3067</t>
-  </si>
-  <si>
-    <t>SDH-1059</t>
-  </si>
-  <si>
-    <t>Ibrahim Al Mutairi</t>
-  </si>
-  <si>
-    <t>SA51 2060 7139 3481 5189 8975</t>
-  </si>
-  <si>
-    <t>SDH-1060</t>
-  </si>
-  <si>
-    <t>Neha Siddiqui</t>
-  </si>
-  <si>
-    <t>SA37 0575 6452 7477 0178 5577</t>
-  </si>
-  <si>
-    <t>SDH-1061</t>
-  </si>
-  <si>
-    <t>Rakan Al Nasser</t>
-  </si>
-  <si>
-    <t>SA47 1049 9488 0092 5655 7314</t>
-  </si>
-  <si>
-    <t>SDH-1062</t>
-  </si>
-  <si>
-    <t>Munira Al Yami</t>
-  </si>
-  <si>
-    <t>SA41 2046 0003 4983 3392 0695</t>
-  </si>
-  <si>
-    <t>SDH-1063</t>
-  </si>
-  <si>
-    <t>Munira Al Asmari</t>
-  </si>
-  <si>
-    <t>Government Relations</t>
-  </si>
-  <si>
-    <t>SA97 1049 1927 9686 2893 2457</t>
-  </si>
-  <si>
-    <t>SDH-1064</t>
-  </si>
-  <si>
-    <t>Nasser Al Muqbel</t>
-  </si>
-  <si>
-    <t>SA52 1022 0482 1074 6859 0026</t>
-  </si>
-  <si>
     <t>SDH-1065</t>
   </si>
   <si>
-    <t>Fadi Shawky</t>
+    <t>Mostafa Mansour</t>
   </si>
   <si>
     <t>SA16 8060 8010 1675 1900 0123</t>
@@ -1451,10 +1451,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -1463,45 +1463,45 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>15700</v>
+        <v>13100</v>
       </c>
       <c r="H7" s="1">
-        <v>3925</v>
+        <v>3275</v>
       </c>
       <c r="I7" s="1">
-        <v>1570</v>
+        <v>1310</v>
       </c>
       <c r="J7" s="1">
-        <v>21195</v>
+        <v>17685</v>
       </c>
       <c r="K7" s="1">
-        <v>1913.44</v>
+        <v>1596.56</v>
       </c>
       <c r="L7" s="1">
-        <v>1913.44</v>
+        <v>1596.56</v>
       </c>
       <c r="M7" s="1">
-        <v>19281.56</v>
+        <v>16088.44</v>
       </c>
       <c r="N7" s="1">
-        <v>2305.94</v>
+        <v>1924.06</v>
       </c>
       <c r="O7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -1513,48 +1513,48 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>13100</v>
+        <v>15600</v>
       </c>
       <c r="H8" s="1">
-        <v>3275</v>
+        <v>3900</v>
       </c>
       <c r="I8" s="1">
-        <v>1310</v>
+        <v>1560</v>
       </c>
       <c r="J8" s="1">
-        <v>17685</v>
+        <v>21060</v>
       </c>
       <c r="K8" s="1">
-        <v>1596.56</v>
+        <v>1901.25</v>
       </c>
       <c r="L8" s="1">
-        <v>1596.56</v>
+        <v>1901.25</v>
       </c>
       <c r="M8" s="1">
-        <v>16088.44</v>
+        <v>19158.75</v>
       </c>
       <c r="N8" s="1">
-        <v>1924.06</v>
+        <v>2291.25</v>
       </c>
       <c r="O8" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="P8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E9">
         <v>30</v>
@@ -1563,48 +1563,48 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>15600</v>
+        <v>9650</v>
       </c>
       <c r="H9" s="1">
-        <v>3900</v>
+        <v>2413</v>
       </c>
       <c r="I9" s="1">
-        <v>1560</v>
+        <v>965</v>
       </c>
       <c r="J9" s="1">
-        <v>21060</v>
+        <v>13028</v>
       </c>
       <c r="K9" s="1">
-        <v>1901.25</v>
+        <v>1176.14</v>
       </c>
       <c r="L9" s="1">
-        <v>1901.25</v>
+        <v>1176.14</v>
       </c>
       <c r="M9" s="1">
-        <v>19158.75</v>
+        <v>11851.86</v>
       </c>
       <c r="N9" s="1">
-        <v>2291.25</v>
+        <v>1417.4</v>
       </c>
       <c r="O9" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="P9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -1613,48 +1613,48 @@
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>9650</v>
+        <v>34150</v>
       </c>
       <c r="H10" s="1">
-        <v>2413</v>
+        <v>8538</v>
       </c>
       <c r="I10" s="1">
-        <v>965</v>
+        <v>3415</v>
       </c>
       <c r="J10" s="1">
-        <v>13028</v>
+        <v>46103</v>
       </c>
       <c r="K10" s="1">
-        <v>1176.14</v>
+        <v>4162.08</v>
       </c>
       <c r="L10" s="1">
-        <v>1176.14</v>
+        <v>4162.08</v>
       </c>
       <c r="M10" s="1">
-        <v>11851.86</v>
+        <v>41940.92</v>
       </c>
       <c r="N10" s="1">
-        <v>1417.4</v>
+        <v>5015.84</v>
       </c>
       <c r="O10" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="P10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E11">
         <v>30</v>
@@ -1663,48 +1663,48 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>34150</v>
+        <v>18250</v>
       </c>
       <c r="H11" s="1">
-        <v>8538</v>
+        <v>4563</v>
       </c>
       <c r="I11" s="1">
-        <v>3415</v>
+        <v>1825</v>
       </c>
       <c r="J11" s="1">
-        <v>46103</v>
+        <v>24638</v>
       </c>
       <c r="K11" s="1">
-        <v>4162.08</v>
+        <v>2224.27</v>
       </c>
       <c r="L11" s="1">
-        <v>4162.08</v>
+        <v>2224.27</v>
       </c>
       <c r="M11" s="1">
-        <v>41940.92</v>
+        <v>22413.73</v>
       </c>
       <c r="N11" s="1">
-        <v>5015.84</v>
+        <v>2680.53</v>
       </c>
       <c r="O11" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>30</v>
@@ -1713,48 +1713,48 @@
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>18250</v>
+        <v>29200</v>
       </c>
       <c r="H12" s="1">
-        <v>4563</v>
+        <v>7300</v>
       </c>
       <c r="I12" s="1">
-        <v>1825</v>
+        <v>2920</v>
       </c>
       <c r="J12" s="1">
-        <v>24638</v>
+        <v>39420</v>
       </c>
       <c r="K12" s="1">
-        <v>2224.27</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>2224.27</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>22413.73</v>
+        <v>39420</v>
       </c>
       <c r="N12" s="1">
-        <v>2680.53</v>
+        <v>730</v>
       </c>
       <c r="O12" t="s">
         <v>20</v>
       </c>
       <c r="P12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <v>30</v>
@@ -1763,48 +1763,48 @@
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>29200</v>
+        <v>41550</v>
       </c>
       <c r="H13" s="1">
-        <v>7300</v>
+        <v>10388</v>
       </c>
       <c r="I13" s="1">
-        <v>2920</v>
+        <v>4155</v>
       </c>
       <c r="J13" s="1">
-        <v>39420</v>
+        <v>56093</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>4387.5</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>4387.5</v>
       </c>
       <c r="M13" s="1">
-        <v>39420</v>
+        <v>51705.5</v>
       </c>
       <c r="N13" s="1">
-        <v>730</v>
+        <v>5287.5</v>
       </c>
       <c r="O13" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E14">
         <v>30</v>
@@ -1813,48 +1813,48 @@
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>41550</v>
+        <v>5500</v>
       </c>
       <c r="H14" s="1">
-        <v>10388</v>
+        <v>1375</v>
       </c>
       <c r="I14" s="1">
-        <v>4155</v>
+        <v>550</v>
       </c>
       <c r="J14" s="1">
-        <v>56093</v>
+        <v>7425</v>
       </c>
       <c r="K14" s="1">
-        <v>4387.5</v>
+        <v>670.31</v>
       </c>
       <c r="L14" s="1">
-        <v>4387.5</v>
+        <v>670.31</v>
       </c>
       <c r="M14" s="1">
-        <v>51705.5</v>
+        <v>6754.69</v>
       </c>
       <c r="N14" s="1">
-        <v>5287.5</v>
+        <v>807.81</v>
       </c>
       <c r="O14" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>30</v>
@@ -1863,48 +1863,48 @@
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>5500</v>
+        <v>7150</v>
       </c>
       <c r="H15" s="1">
-        <v>1375</v>
+        <v>1788</v>
       </c>
       <c r="I15" s="1">
-        <v>550</v>
+        <v>715</v>
       </c>
       <c r="J15" s="1">
-        <v>7425</v>
+        <v>9653</v>
       </c>
       <c r="K15" s="1">
-        <v>670.31</v>
+        <v>871.46</v>
       </c>
       <c r="L15" s="1">
-        <v>670.31</v>
+        <v>871.46</v>
       </c>
       <c r="M15" s="1">
-        <v>6754.69</v>
+        <v>8781.54</v>
       </c>
       <c r="N15" s="1">
-        <v>807.81</v>
+        <v>1050.21</v>
       </c>
       <c r="O15" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="E16">
         <v>30</v>
@@ -1913,31 +1913,31 @@
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>7150</v>
+        <v>26550</v>
       </c>
       <c r="H16" s="1">
-        <v>1788</v>
+        <v>6638</v>
       </c>
       <c r="I16" s="1">
-        <v>715</v>
+        <v>2655</v>
       </c>
       <c r="J16" s="1">
-        <v>9653</v>
+        <v>35843</v>
       </c>
       <c r="K16" s="1">
-        <v>871.46</v>
+        <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>871.46</v>
+        <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>8781.54</v>
+        <v>35843</v>
       </c>
       <c r="N16" s="1">
-        <v>1050.21</v>
+        <v>663.76</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="P16" t="s">
         <v>82</v>
@@ -1951,10 +1951,10 @@
         <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="E17">
         <v>30</v>
@@ -1963,48 +1963,48 @@
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>26550</v>
+        <v>19000</v>
       </c>
       <c r="H17" s="1">
-        <v>6638</v>
+        <v>4750</v>
       </c>
       <c r="I17" s="1">
-        <v>2655</v>
+        <v>1900</v>
       </c>
       <c r="J17" s="1">
-        <v>35843</v>
+        <v>25650</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>2315.63</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>2315.63</v>
       </c>
       <c r="M17" s="1">
-        <v>35843</v>
+        <v>23334.37</v>
       </c>
       <c r="N17" s="1">
-        <v>663.76</v>
+        <v>2790.63</v>
       </c>
       <c r="O17" t="s">
         <v>20</v>
       </c>
       <c r="P17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="E18">
         <v>30</v>
@@ -2013,31 +2013,31 @@
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>19000</v>
+        <v>16450</v>
       </c>
       <c r="H18" s="1">
-        <v>4750</v>
+        <v>4113</v>
       </c>
       <c r="I18" s="1">
-        <v>1900</v>
+        <v>1645</v>
       </c>
       <c r="J18" s="1">
-        <v>25650</v>
+        <v>22208</v>
       </c>
       <c r="K18" s="1">
-        <v>2315.63</v>
+        <v>2004.89</v>
       </c>
       <c r="L18" s="1">
-        <v>2315.63</v>
+        <v>2004.89</v>
       </c>
       <c r="M18" s="1">
-        <v>23334.37</v>
+        <v>20203.11</v>
       </c>
       <c r="N18" s="1">
-        <v>2790.63</v>
+        <v>2416.15</v>
       </c>
       <c r="O18" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P18" t="s">
         <v>89</v>
@@ -2051,10 +2051,10 @@
         <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="E19">
         <v>30</v>
@@ -2063,48 +2063,48 @@
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>16450</v>
+        <v>68400</v>
       </c>
       <c r="H19" s="1">
-        <v>4113</v>
+        <v>17100</v>
       </c>
       <c r="I19" s="1">
-        <v>1645</v>
+        <v>6840</v>
       </c>
       <c r="J19" s="1">
-        <v>22208</v>
+        <v>92340</v>
       </c>
       <c r="K19" s="1">
-        <v>2004.89</v>
+        <v>4387.5</v>
       </c>
       <c r="L19" s="1">
-        <v>2004.89</v>
+        <v>4387.5</v>
       </c>
       <c r="M19" s="1">
-        <v>20203.11</v>
+        <v>87952.5</v>
       </c>
       <c r="N19" s="1">
-        <v>2416.15</v>
+        <v>5287.5</v>
       </c>
       <c r="O19" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="P19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="E20">
         <v>30</v>
@@ -2113,31 +2113,31 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>68400</v>
+        <v>7850</v>
       </c>
       <c r="H20" s="1">
-        <v>17100</v>
+        <v>1963</v>
       </c>
       <c r="I20" s="1">
-        <v>6840</v>
+        <v>785</v>
       </c>
       <c r="J20" s="1">
-        <v>92340</v>
+        <v>10598</v>
       </c>
       <c r="K20" s="1">
-        <v>4387.5</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>4387.5</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>87952.5</v>
+        <v>10598</v>
       </c>
       <c r="N20" s="1">
-        <v>5287.5</v>
+        <v>196.26</v>
       </c>
       <c r="O20" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="P20" t="s">
         <v>97</v>
@@ -2151,10 +2151,10 @@
         <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <v>30</v>
@@ -2163,31 +2163,31 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>7850</v>
+        <v>47700</v>
       </c>
       <c r="H21" s="1">
-        <v>1963</v>
+        <v>11925</v>
       </c>
       <c r="I21" s="1">
-        <v>785</v>
+        <v>4770</v>
       </c>
       <c r="J21" s="1">
-        <v>10598</v>
+        <v>64395</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>4387.5</v>
       </c>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>4387.5</v>
       </c>
       <c r="M21" s="1">
-        <v>10598</v>
+        <v>60007.5</v>
       </c>
       <c r="N21" s="1">
-        <v>196.26</v>
+        <v>5287.5</v>
       </c>
       <c r="O21" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="P21" t="s">
         <v>100</v>
@@ -2204,7 +2204,7 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="E22">
         <v>30</v>
@@ -2213,31 +2213,31 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>47700</v>
+        <v>16050</v>
       </c>
       <c r="H22" s="1">
-        <v>11925</v>
+        <v>4013</v>
       </c>
       <c r="I22" s="1">
-        <v>4770</v>
+        <v>1605</v>
       </c>
       <c r="J22" s="1">
-        <v>64395</v>
+        <v>21668</v>
       </c>
       <c r="K22" s="1">
-        <v>4387.5</v>
+        <v>1956.14</v>
       </c>
       <c r="L22" s="1">
-        <v>4387.5</v>
+        <v>1956.14</v>
       </c>
       <c r="M22" s="1">
-        <v>60007.5</v>
+        <v>19711.86</v>
       </c>
       <c r="N22" s="1">
-        <v>5287.5</v>
+        <v>2357.4</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P22" t="s">
         <v>103</v>
@@ -2251,10 +2251,10 @@
         <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="E23">
         <v>30</v>
@@ -2263,28 +2263,28 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>16050</v>
+        <v>5800</v>
       </c>
       <c r="H23" s="1">
-        <v>4013</v>
+        <v>1450</v>
       </c>
       <c r="I23" s="1">
-        <v>1605</v>
+        <v>580</v>
       </c>
       <c r="J23" s="1">
-        <v>21668</v>
+        <v>7830</v>
       </c>
       <c r="K23" s="1">
-        <v>1956.14</v>
+        <v>706.88</v>
       </c>
       <c r="L23" s="1">
-        <v>1956.14</v>
+        <v>706.88</v>
       </c>
       <c r="M23" s="1">
-        <v>19711.86</v>
+        <v>7123.12</v>
       </c>
       <c r="N23" s="1">
-        <v>2357.4</v>
+        <v>851.88</v>
       </c>
       <c r="O23" t="s">
         <v>24</v>
@@ -2301,10 +2301,10 @@
         <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E24">
         <v>30</v>
@@ -2313,48 +2313,48 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>5800</v>
+        <v>12250</v>
       </c>
       <c r="H24" s="1">
-        <v>1450</v>
+        <v>3063</v>
       </c>
       <c r="I24" s="1">
-        <v>580</v>
+        <v>1225</v>
       </c>
       <c r="J24" s="1">
-        <v>7830</v>
+        <v>16538</v>
       </c>
       <c r="K24" s="1">
-        <v>706.88</v>
+        <v>1493.02</v>
       </c>
       <c r="L24" s="1">
-        <v>706.88</v>
+        <v>1493.02</v>
       </c>
       <c r="M24" s="1">
-        <v>7123.12</v>
+        <v>15044.98</v>
       </c>
       <c r="N24" s="1">
-        <v>851.88</v>
+        <v>1799.28</v>
       </c>
       <c r="O24" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E25">
         <v>30</v>
@@ -2363,31 +2363,31 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>12250</v>
+        <v>12950</v>
       </c>
       <c r="H25" s="1">
-        <v>3063</v>
+        <v>3238</v>
       </c>
       <c r="I25" s="1">
-        <v>1225</v>
+        <v>1295</v>
       </c>
       <c r="J25" s="1">
-        <v>16538</v>
+        <v>17483</v>
       </c>
       <c r="K25" s="1">
-        <v>1493.02</v>
+        <v>0</v>
       </c>
       <c r="L25" s="1">
-        <v>1493.02</v>
+        <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>15044.98</v>
+        <v>17483</v>
       </c>
       <c r="N25" s="1">
-        <v>1799.28</v>
+        <v>323.76</v>
       </c>
       <c r="O25" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="P25" t="s">
         <v>113</v>
@@ -2401,10 +2401,10 @@
         <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="E26">
         <v>30</v>
@@ -2413,31 +2413,31 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>12950</v>
+        <v>27700</v>
       </c>
       <c r="H26" s="1">
-        <v>3238</v>
+        <v>6925</v>
       </c>
       <c r="I26" s="1">
-        <v>1295</v>
+        <v>2770</v>
       </c>
       <c r="J26" s="1">
-        <v>17483</v>
+        <v>37395</v>
       </c>
       <c r="K26" s="1">
-        <v>0</v>
+        <v>3375.94</v>
       </c>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>3375.94</v>
       </c>
       <c r="M26" s="1">
-        <v>17483</v>
+        <v>34019.06</v>
       </c>
       <c r="N26" s="1">
-        <v>323.76</v>
+        <v>4068.44</v>
       </c>
       <c r="O26" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P26" t="s">
         <v>116</v>
@@ -2445,16 +2445,16 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="E27">
         <v>30</v>
@@ -2463,48 +2463,48 @@
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>27700</v>
+        <v>9850</v>
       </c>
       <c r="H27" s="1">
-        <v>6925</v>
+        <v>2463</v>
       </c>
       <c r="I27" s="1">
-        <v>2770</v>
+        <v>985</v>
       </c>
       <c r="J27" s="1">
-        <v>37395</v>
+        <v>13298</v>
       </c>
       <c r="K27" s="1">
-        <v>3375.94</v>
+        <v>1200.52</v>
       </c>
       <c r="L27" s="1">
-        <v>3375.94</v>
+        <v>1200.52</v>
       </c>
       <c r="M27" s="1">
-        <v>34019.06</v>
+        <v>12097.48</v>
       </c>
       <c r="N27" s="1">
-        <v>4068.44</v>
+        <v>1446.78</v>
       </c>
       <c r="O27" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="P27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E28">
         <v>30</v>
@@ -2513,48 +2513,48 @@
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>9850</v>
+        <v>16900</v>
       </c>
       <c r="H28" s="1">
-        <v>2463</v>
+        <v>4225</v>
       </c>
       <c r="I28" s="1">
-        <v>985</v>
+        <v>1690</v>
       </c>
       <c r="J28" s="1">
-        <v>13298</v>
+        <v>22815</v>
       </c>
       <c r="K28" s="1">
-        <v>1200.52</v>
+        <v>0</v>
       </c>
       <c r="L28" s="1">
-        <v>1200.52</v>
+        <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>12097.48</v>
+        <v>22815</v>
       </c>
       <c r="N28" s="1">
-        <v>1446.78</v>
+        <v>422.5</v>
       </c>
       <c r="O28" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="P28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="E29">
         <v>30</v>
@@ -2563,48 +2563,48 @@
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>16900</v>
+        <v>6100</v>
       </c>
       <c r="H29" s="1">
-        <v>4225</v>
+        <v>1525</v>
       </c>
       <c r="I29" s="1">
-        <v>1690</v>
+        <v>610</v>
       </c>
       <c r="J29" s="1">
-        <v>22815</v>
+        <v>8235</v>
       </c>
       <c r="K29" s="1">
-        <v>0</v>
+        <v>743.44</v>
       </c>
       <c r="L29" s="1">
-        <v>0</v>
+        <v>743.44</v>
       </c>
       <c r="M29" s="1">
-        <v>22815</v>
+        <v>7491.56</v>
       </c>
       <c r="N29" s="1">
-        <v>422.5</v>
+        <v>895.94</v>
       </c>
       <c r="O29" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="P29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E30">
         <v>30</v>
@@ -2613,48 +2613,48 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>6100</v>
+        <v>12650</v>
       </c>
       <c r="H30" s="1">
-        <v>1525</v>
+        <v>3163</v>
       </c>
       <c r="I30" s="1">
-        <v>610</v>
+        <v>1265</v>
       </c>
       <c r="J30" s="1">
-        <v>8235</v>
+        <v>17078</v>
       </c>
       <c r="K30" s="1">
-        <v>743.44</v>
+        <v>1541.77</v>
       </c>
       <c r="L30" s="1">
-        <v>743.44</v>
+        <v>1541.77</v>
       </c>
       <c r="M30" s="1">
-        <v>7491.56</v>
+        <v>15536.23</v>
       </c>
       <c r="N30" s="1">
-        <v>895.94</v>
+        <v>1858.03</v>
       </c>
       <c r="O30" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="P30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -2663,48 +2663,48 @@
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>12650</v>
+        <v>7950</v>
       </c>
       <c r="H31" s="1">
-        <v>3163</v>
+        <v>1988</v>
       </c>
       <c r="I31" s="1">
-        <v>1265</v>
+        <v>795</v>
       </c>
       <c r="J31" s="1">
-        <v>17078</v>
+        <v>10733</v>
       </c>
       <c r="K31" s="1">
-        <v>1541.77</v>
+        <v>968.96</v>
       </c>
       <c r="L31" s="1">
-        <v>1541.77</v>
+        <v>968.96</v>
       </c>
       <c r="M31" s="1">
-        <v>15536.23</v>
+        <v>9764.04</v>
       </c>
       <c r="N31" s="1">
-        <v>1858.03</v>
+        <v>1167.71</v>
       </c>
       <c r="O31" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E32">
         <v>30</v>
@@ -2713,48 +2713,48 @@
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>7950</v>
+        <v>31000</v>
       </c>
       <c r="H32" s="1">
-        <v>1988</v>
+        <v>7750</v>
       </c>
       <c r="I32" s="1">
-        <v>795</v>
+        <v>3100</v>
       </c>
       <c r="J32" s="1">
-        <v>10733</v>
+        <v>41850</v>
       </c>
       <c r="K32" s="1">
-        <v>968.96</v>
+        <v>3778.13</v>
       </c>
       <c r="L32" s="1">
-        <v>968.96</v>
+        <v>3778.13</v>
       </c>
       <c r="M32" s="1">
-        <v>9764.04</v>
+        <v>38071.87</v>
       </c>
       <c r="N32" s="1">
-        <v>1167.71</v>
+        <v>4553.13</v>
       </c>
       <c r="O32" t="s">
         <v>24</v>
       </c>
       <c r="P32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E33">
         <v>30</v>
@@ -2763,48 +2763,48 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>31000</v>
+        <v>8150</v>
       </c>
       <c r="H33" s="1">
-        <v>7750</v>
+        <v>2038</v>
       </c>
       <c r="I33" s="1">
-        <v>3100</v>
+        <v>815</v>
       </c>
       <c r="J33" s="1">
-        <v>41850</v>
+        <v>11003</v>
       </c>
       <c r="K33" s="1">
-        <v>3778.13</v>
+        <v>993.33</v>
       </c>
       <c r="L33" s="1">
-        <v>3778.13</v>
+        <v>993.33</v>
       </c>
       <c r="M33" s="1">
-        <v>38071.87</v>
+        <v>10009.67</v>
       </c>
       <c r="N33" s="1">
-        <v>4553.13</v>
+        <v>1197.09</v>
       </c>
       <c r="O33" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E34">
         <v>30</v>
@@ -2813,48 +2813,48 @@
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>8150</v>
+        <v>18750</v>
       </c>
       <c r="H34" s="1">
-        <v>2038</v>
+        <v>4688</v>
       </c>
       <c r="I34" s="1">
-        <v>815</v>
+        <v>1875</v>
       </c>
       <c r="J34" s="1">
-        <v>11003</v>
+        <v>25313</v>
       </c>
       <c r="K34" s="1">
-        <v>993.33</v>
+        <v>2285.21</v>
       </c>
       <c r="L34" s="1">
-        <v>993.33</v>
+        <v>2285.21</v>
       </c>
       <c r="M34" s="1">
-        <v>10009.67</v>
+        <v>23027.79</v>
       </c>
       <c r="N34" s="1">
-        <v>1197.09</v>
+        <v>2753.96</v>
       </c>
       <c r="O34" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E35">
         <v>30</v>
@@ -2863,48 +2863,48 @@
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>18750</v>
+        <v>7850</v>
       </c>
       <c r="H35" s="1">
-        <v>4688</v>
+        <v>1963</v>
       </c>
       <c r="I35" s="1">
-        <v>1875</v>
+        <v>785</v>
       </c>
       <c r="J35" s="1">
-        <v>25313</v>
+        <v>10598</v>
       </c>
       <c r="K35" s="1">
-        <v>2285.21</v>
+        <v>956.77</v>
       </c>
       <c r="L35" s="1">
-        <v>2285.21</v>
+        <v>956.77</v>
       </c>
       <c r="M35" s="1">
-        <v>23027.79</v>
+        <v>9641.23</v>
       </c>
       <c r="N35" s="1">
-        <v>2753.96</v>
+        <v>1153.03</v>
       </c>
       <c r="O35" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="P35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="E36">
         <v>30</v>
@@ -2913,48 +2913,48 @@
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>7850</v>
+        <v>12800</v>
       </c>
       <c r="H36" s="1">
-        <v>1963</v>
+        <v>3200</v>
       </c>
       <c r="I36" s="1">
-        <v>785</v>
+        <v>1280</v>
       </c>
       <c r="J36" s="1">
-        <v>10598</v>
+        <v>17280</v>
       </c>
       <c r="K36" s="1">
-        <v>956.77</v>
+        <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>956.77</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>9641.23</v>
+        <v>17280</v>
       </c>
       <c r="N36" s="1">
-        <v>1153.03</v>
+        <v>320</v>
       </c>
       <c r="O36" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="P36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="E37">
         <v>30</v>
@@ -2963,48 +2963,48 @@
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>12800</v>
+        <v>8200</v>
       </c>
       <c r="H37" s="1">
-        <v>3200</v>
+        <v>2050</v>
       </c>
       <c r="I37" s="1">
-        <v>1280</v>
+        <v>820</v>
       </c>
       <c r="J37" s="1">
-        <v>17280</v>
+        <v>11070</v>
       </c>
       <c r="K37" s="1">
-        <v>0</v>
+        <v>999.38</v>
       </c>
       <c r="L37" s="1">
-        <v>0</v>
+        <v>999.38</v>
       </c>
       <c r="M37" s="1">
-        <v>17280</v>
+        <v>10070.62</v>
       </c>
       <c r="N37" s="1">
-        <v>320</v>
+        <v>1204.38</v>
       </c>
       <c r="O37" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="P37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="E38">
         <v>30</v>
@@ -3013,48 +3013,48 @@
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>8200</v>
+        <v>28600</v>
       </c>
       <c r="H38" s="1">
-        <v>2050</v>
+        <v>7150</v>
       </c>
       <c r="I38" s="1">
-        <v>820</v>
+        <v>2860</v>
       </c>
       <c r="J38" s="1">
-        <v>11070</v>
+        <v>38610</v>
       </c>
       <c r="K38" s="1">
-        <v>999.38</v>
+        <v>0</v>
       </c>
       <c r="L38" s="1">
-        <v>999.38</v>
+        <v>0</v>
       </c>
       <c r="M38" s="1">
-        <v>10070.62</v>
+        <v>38610</v>
       </c>
       <c r="N38" s="1">
-        <v>1204.38</v>
+        <v>715</v>
       </c>
       <c r="O38" t="s">
         <v>20</v>
       </c>
       <c r="P38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E39">
         <v>30</v>
@@ -3063,16 +3063,16 @@
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>28600</v>
+        <v>14500</v>
       </c>
       <c r="H39" s="1">
-        <v>7150</v>
+        <v>3625</v>
       </c>
       <c r="I39" s="1">
-        <v>2860</v>
+        <v>1450</v>
       </c>
       <c r="J39" s="1">
-        <v>38610</v>
+        <v>19575</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -3081,30 +3081,30 @@
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>38610</v>
+        <v>19575</v>
       </c>
       <c r="N39" s="1">
-        <v>715</v>
+        <v>362.5</v>
       </c>
       <c r="O39" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="E40">
         <v>30</v>
@@ -3113,48 +3113,48 @@
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>14500</v>
+        <v>11800</v>
       </c>
       <c r="H40" s="1">
-        <v>3625</v>
+        <v>2950</v>
       </c>
       <c r="I40" s="1">
-        <v>1450</v>
+        <v>1180</v>
       </c>
       <c r="J40" s="1">
-        <v>19575</v>
+        <v>15930</v>
       </c>
       <c r="K40" s="1">
-        <v>0</v>
+        <v>1438.13</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>1438.13</v>
       </c>
       <c r="M40" s="1">
-        <v>19575</v>
+        <v>14491.87</v>
       </c>
       <c r="N40" s="1">
-        <v>362.5</v>
+        <v>1733.13</v>
       </c>
       <c r="O40" t="s">
         <v>24</v>
       </c>
       <c r="P40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="E41">
         <v>30</v>
@@ -3163,48 +3163,48 @@
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>11800</v>
+        <v>8700</v>
       </c>
       <c r="H41" s="1">
-        <v>2950</v>
+        <v>2175</v>
       </c>
       <c r="I41" s="1">
-        <v>1180</v>
+        <v>870</v>
       </c>
       <c r="J41" s="1">
-        <v>15930</v>
+        <v>11745</v>
       </c>
       <c r="K41" s="1">
-        <v>1438.13</v>
+        <v>1060.31</v>
       </c>
       <c r="L41" s="1">
-        <v>1438.13</v>
+        <v>1060.31</v>
       </c>
       <c r="M41" s="1">
-        <v>14491.87</v>
+        <v>10684.69</v>
       </c>
       <c r="N41" s="1">
-        <v>1733.13</v>
+        <v>1277.81</v>
       </c>
       <c r="O41" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="E42">
         <v>30</v>
@@ -3213,48 +3213,48 @@
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>8700</v>
+        <v>28650</v>
       </c>
       <c r="H42" s="1">
-        <v>2175</v>
+        <v>7163</v>
       </c>
       <c r="I42" s="1">
-        <v>870</v>
+        <v>2865</v>
       </c>
       <c r="J42" s="1">
-        <v>11745</v>
+        <v>38678</v>
       </c>
       <c r="K42" s="1">
-        <v>1060.31</v>
+        <v>3491.77</v>
       </c>
       <c r="L42" s="1">
-        <v>1060.31</v>
+        <v>3491.77</v>
       </c>
       <c r="M42" s="1">
-        <v>10684.69</v>
+        <v>35186.23</v>
       </c>
       <c r="N42" s="1">
-        <v>1277.81</v>
+        <v>4208.03</v>
       </c>
       <c r="O42" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="P42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
         <v>166</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E43">
         <v>30</v>
@@ -3263,31 +3263,31 @@
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>28650</v>
+        <v>17950</v>
       </c>
       <c r="H43" s="1">
-        <v>7163</v>
+        <v>4488</v>
       </c>
       <c r="I43" s="1">
-        <v>2865</v>
+        <v>1795</v>
       </c>
       <c r="J43" s="1">
-        <v>38678</v>
+        <v>24233</v>
       </c>
       <c r="K43" s="1">
-        <v>3491.77</v>
+        <v>2187.71</v>
       </c>
       <c r="L43" s="1">
-        <v>3491.77</v>
+        <v>2187.71</v>
       </c>
       <c r="M43" s="1">
-        <v>35186.23</v>
+        <v>22045.29</v>
       </c>
       <c r="N43" s="1">
-        <v>4208.03</v>
+        <v>2636.46</v>
       </c>
       <c r="O43" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="P43" t="s">
         <v>167</v>
@@ -3301,10 +3301,10 @@
         <v>169</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="E44">
         <v>30</v>
@@ -3313,31 +3313,31 @@
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>17950</v>
+        <v>7650</v>
       </c>
       <c r="H44" s="1">
-        <v>4488</v>
+        <v>1913</v>
       </c>
       <c r="I44" s="1">
-        <v>1795</v>
+        <v>765</v>
       </c>
       <c r="J44" s="1">
-        <v>24233</v>
+        <v>10328</v>
       </c>
       <c r="K44" s="1">
-        <v>2187.71</v>
+        <v>1028.02</v>
       </c>
       <c r="L44" s="1">
-        <v>2187.71</v>
+        <v>1028.02</v>
       </c>
       <c r="M44" s="1">
-        <v>22045.29</v>
+        <v>9299.98</v>
       </c>
       <c r="N44" s="1">
-        <v>2636.46</v>
+        <v>1219.28</v>
       </c>
       <c r="O44" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="P44" t="s">
         <v>170</v>
@@ -3351,10 +3351,10 @@
         <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="E45">
         <v>30</v>
@@ -3363,31 +3363,31 @@
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>7650</v>
+        <v>13650</v>
       </c>
       <c r="H45" s="1">
-        <v>1913</v>
+        <v>3413</v>
       </c>
       <c r="I45" s="1">
-        <v>765</v>
+        <v>1365</v>
       </c>
       <c r="J45" s="1">
-        <v>10328</v>
+        <v>18428</v>
       </c>
       <c r="K45" s="1">
-        <v>1028.02</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>1028.02</v>
+        <v>0</v>
       </c>
       <c r="M45" s="1">
-        <v>9299.98</v>
+        <v>18428</v>
       </c>
       <c r="N45" s="1">
-        <v>1219.28</v>
+        <v>341.26</v>
       </c>
       <c r="O45" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="P45" t="s">
         <v>173</v>
@@ -3401,7 +3401,7 @@
         <v>175</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -3413,28 +3413,28 @@
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>13650</v>
+        <v>15050</v>
       </c>
       <c r="H46" s="1">
-        <v>3413</v>
+        <v>3763</v>
       </c>
       <c r="I46" s="1">
-        <v>1365</v>
+        <v>1505</v>
       </c>
       <c r="J46" s="1">
-        <v>18428</v>
+        <v>20318</v>
       </c>
       <c r="K46" s="1">
-        <v>0</v>
+        <v>2022.4</v>
       </c>
       <c r="L46" s="1">
-        <v>0</v>
+        <v>2022.4</v>
       </c>
       <c r="M46" s="1">
-        <v>18428</v>
+        <v>18295.6</v>
       </c>
       <c r="N46" s="1">
-        <v>341.26</v>
+        <v>2398.66</v>
       </c>
       <c r="O46" t="s">
         <v>24</v>
@@ -3454,7 +3454,7 @@
         <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E47">
         <v>30</v>
@@ -3501,10 +3501,10 @@
         <v>181</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E48">
         <v>30</v>
@@ -3551,10 +3551,10 @@
         <v>184</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E49">
         <v>30</v>
@@ -3601,10 +3601,10 @@
         <v>188</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E50">
         <v>30</v>
@@ -3637,7 +3637,7 @@
         <v>187.5</v>
       </c>
       <c r="O50" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P50" t="s">
         <v>189</v>
@@ -3687,7 +3687,7 @@
         <v>2653.66</v>
       </c>
       <c r="O51" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P51" t="s">
         <v>192</v>
@@ -3704,7 +3704,7 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="E52">
         <v>30</v>
@@ -3713,28 +3713,28 @@
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>12600</v>
+        <v>15700</v>
       </c>
       <c r="H52" s="1">
-        <v>3150</v>
+        <v>3925</v>
       </c>
       <c r="I52" s="1">
-        <v>1260</v>
+        <v>1570</v>
       </c>
       <c r="J52" s="1">
-        <v>17010</v>
+        <v>21195</v>
       </c>
       <c r="K52" s="1">
-        <v>1535.63</v>
+        <v>1913.44</v>
       </c>
       <c r="L52" s="1">
-        <v>1535.63</v>
+        <v>1913.44</v>
       </c>
       <c r="M52" s="1">
-        <v>15474.37</v>
+        <v>19281.56</v>
       </c>
       <c r="N52" s="1">
-        <v>1850.63</v>
+        <v>2305.94</v>
       </c>
       <c r="O52" t="s">
         <v>20</v>
@@ -3751,10 +3751,10 @@
         <v>197</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E53">
         <v>30</v>
@@ -3801,10 +3801,10 @@
         <v>200</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D54" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E54">
         <v>30</v>
@@ -3851,7 +3851,7 @@
         <v>203</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
         <v>29</v>
@@ -3901,10 +3901,10 @@
         <v>206</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E56">
         <v>30</v>
@@ -3951,7 +3951,7 @@
         <v>209</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D57" t="s">
         <v>33</v>
@@ -4001,7 +4001,7 @@
         <v>212</v>
       </c>
       <c r="C58" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D58" t="s">
         <v>29</v>
@@ -4037,7 +4037,7 @@
         <v>2087.81</v>
       </c>
       <c r="O58" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P58" t="s">
         <v>213</v>
@@ -4051,10 +4051,10 @@
         <v>215</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E59">
         <v>30</v>
@@ -4101,7 +4101,7 @@
         <v>218</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
         <v>29</v>
@@ -4137,7 +4137,7 @@
         <v>2486.25</v>
       </c>
       <c r="O60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P60" t="s">
         <v>219</v>
@@ -4151,10 +4151,10 @@
         <v>221</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E61">
         <v>30</v>
@@ -4187,7 +4187,7 @@
         <v>241.26</v>
       </c>
       <c r="O61" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P61" t="s">
         <v>222</v>
@@ -4201,10 +4201,10 @@
         <v>224</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D62" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E62">
         <v>30</v>
@@ -4251,10 +4251,10 @@
         <v>227</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E63">
         <v>30</v>
@@ -4287,7 +4287,7 @@
         <v>1577.81</v>
       </c>
       <c r="O63" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P63" t="s">
         <v>228</v>
@@ -4304,7 +4304,7 @@
         <v>231</v>
       </c>
       <c r="D64" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>30</v>
@@ -4351,10 +4351,10 @@
         <v>234</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="E65">
         <v>30</v>
@@ -4363,31 +4363,31 @@
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>15050</v>
+        <v>12600</v>
       </c>
       <c r="H65" s="1">
-        <v>3763</v>
+        <v>3150</v>
       </c>
       <c r="I65" s="1">
-        <v>1505</v>
+        <v>1260</v>
       </c>
       <c r="J65" s="1">
-        <v>20318</v>
+        <v>17010</v>
       </c>
       <c r="K65" s="1">
-        <v>2022.4</v>
+        <v>1693.13</v>
       </c>
       <c r="L65" s="1">
-        <v>2022.4</v>
+        <v>1693.13</v>
       </c>
       <c r="M65" s="1">
-        <v>18295.6</v>
+        <v>15316.87</v>
       </c>
       <c r="N65" s="1">
-        <v>2398.66</v>
+        <v>2008.13</v>
       </c>
       <c r="O65" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P65" t="s">
         <v>235</v>
@@ -4401,10 +4401,10 @@
         <v>237</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E66">
         <v>30</v>
@@ -4467,16 +4467,16 @@
         <v>1459839</v>
       </c>
       <c r="K67" s="5">
-        <v>92715.11</v>
+        <v>92872.61</v>
       </c>
       <c r="L67" s="5">
-        <v>92715.11</v>
+        <v>92872.61</v>
       </c>
       <c r="M67" s="5">
-        <v>1367123.89</v>
+        <v>1366966.39</v>
       </c>
       <c r="N67" s="5">
-        <v>118507.89</v>
+        <v>118665.39</v>
       </c>
       <c r="O67" s="4"/>
       <c r="P67" s="4"/>
